--- a/nr-prepare-release/ig/StructureDefinition-cdl-document-reference.xlsx
+++ b/nr-prepare-release/ig/StructureDefinition-cdl-document-reference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T08:28:57+00:00</t>
+    <t>2026-07-20T08:30:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-prepare-release/ig/StructureDefinition-cdl-document-reference.xlsx
+++ b/nr-prepare-release/ig/StructureDefinition-cdl-document-reference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T08:30:08+00:00</t>
+    <t>2026-07-20T08:39:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>
@@ -660,7 +660,7 @@
     <t>Key metadata element describing the document that describes he exact type of document. Helps humans to assess whether the document is of interest when viewing a list of documents.</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J23-TypeNoteCahierLiaison-CISIS/FHIR/JDV-J23-TypeNoteCahierLiaison-CISIS|1.5.0</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J23-TypeNoteCahierLiaison-CISIS/FHIR/JDV-J23-TypeNoteCahierLiaison-CISIS|20200424120000</t>
   </si>
   <si>
     <t>Note.type</t>
@@ -1055,7 +1055,7 @@
     <t>Use of the Health Care Privacy/Security Classification (HCS) system of security-tag use is recommended.</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J110-StatutVisibiliteDocument-CISIS/FHIR/JDV-J110-StatutVisibiliteDocument-CISIS|1.5.0</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J110-StatutVisibiliteDocument-CISIS/FHIR/JDV-J110-StatutVisibiliteDocument-CISIS|20200424120000</t>
   </si>
   <si>
     <t>Note.restrictionAudience</t>
@@ -1908,7 +1908,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="63.28515625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="98.75390625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="108.75390625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
